--- a/tests/benchmarks/machine1/results_final/reporte_final.xlsx
+++ b/tests/benchmarks/machine1/results_final/reporte_final.xlsx
@@ -13,9 +13,12 @@
     <sheet name="4. Procesos" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Comparacion final" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Efecto compilador" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. OpenMP speedup" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8. OpenMP vs pthreads" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9. Eficiencia paralela" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="7. OpenMP sin opt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. OpenMP con opt" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9. pthreads vs OMP sin opt" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10. pthreads vs OMP con opt" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11. Eficiencia sin opt" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12. Eficiencia con opt" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -380,6 +383,221 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>22</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>22</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -716,7 +934,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5905500" cy="3429000"/>
@@ -741,7 +959,7 @@
     <from>
       <col>11</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5905500" cy="3429000"/>
@@ -807,31 +1025,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>22</col>
-      <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5905500" cy="3429000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3377,6 +3570,4623 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pthreads/best vs OMP/best  |  top 2 pthreads + top 1 OMP  |  ref = seq_std/best</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 1  —  Mediciones individuales (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Secuencial naive con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>30.005</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>312.955</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2540.758</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>36022.321</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>434910.671</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>30.071</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>312.064</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2540.398</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>35590.382</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>344113.604</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>30.091</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>312.066</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2550.371</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>35602.554</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>365954.583</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>30.147</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>312.059</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2543.867</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>35751.773</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>334690.484</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>30.083</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>312.649</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2541.859</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>35526.842</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>341364.101</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>30.026</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>311.893</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2546.591</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>35525.175</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>510874.781</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>30.062</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>312.047</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2541.431</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>35557.655</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>505512.386</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>30.237</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>311.989</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2543.702</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>35225.193</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>502152.475</v>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>311.605</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2539.963</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>35261.713</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>325713.787</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>30.227</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>311.89</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2542.086</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>35340.683</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>325443.173</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>30.119</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>312.122</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2543.103</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>35540.429</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>399073.004</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>3.066</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>223.81</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>76245.927</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>19.11</v>
+      </c>
+    </row>
+    <row r="18" ht="6" customHeight="1">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Concurrencia 6 hilos con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>5.364</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>52.811</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>427.681</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>6087.954</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>79986.159</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>52.641</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>430.247</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>6025.668</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>80510.35400000001</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>5.342</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>53.471</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>434.243</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>5995.036</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>82012.837</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>5.391</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>53.033</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>428.75</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>6098.668</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>81003.02800000001</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>5.348</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>429.429</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>6084.622</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>81305.83100000001</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>5.377</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>428.333</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>6049.848</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>81492.15700000001</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>5.346</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>52.736</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>429.682</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>5999.036</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>82822.33</v>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>5.349</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>52.621</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>429.459</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>5956.608</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>84010.095</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>5.359</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>52.484</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>429.73</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>6035.778</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>82918.28999999999</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>5.342</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>52.642</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>430.19</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>6026.583</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>83987.841</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>52.822</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>429.774</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>6035.98</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>82004.89200000001</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>43.273</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>1323.621</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="34" ht="6" customHeight="1">
+      <c r="A34" s="12" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Concurrencia 12 hilos con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>5.449</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>55.774</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>438.728</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>6161.586</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>83248.595</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>5.501</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>55.498</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>436.098</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>6102.139</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>80585.217</v>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>55.289</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>433.324</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>6046.794</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>81627.19</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>5.479</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>55.436</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>434.354</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>6136.767</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>81365.746</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>5.587</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>55.486</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>434.173</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>6067.791</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>84340.577</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>437.879</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>6091.347</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>82143.193</v>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>5.475</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>55.759</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>437.851</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>6079.568</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>81002.622</v>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>5.477</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>55.871</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>437.771</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>6126.084</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>82819.85799999999</v>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>7.812</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>55.922</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>438.506</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>6168.99</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>82459.068</v>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>5.456</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>55.724</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>438.158</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>6080.506</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>84254.745</v>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>5.722</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>55.632</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>436.684</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>6106.157</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>82384.681</v>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>38.666</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>1228.105</v>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="50" ht="6" customHeight="1">
+      <c r="A50" s="12" t="n"/>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>OpenMP 12 hilos con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>7.316</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>62.489</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>564.903</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>6734.835</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>68260.682</v>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>7.286</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>62.479</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>564.923</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>6721.784</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>68969.21400000001</v>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>7.272</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>62.498</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>565.399</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>6748.11</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>68560.27</v>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>7.327</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>62.501</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>565.028</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>6736.491</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>68834.321</v>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>7.298</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>62.489</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>565.646</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>6741.619</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>69801.397</v>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>7.269</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>62.654</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>564.875</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>6743.477</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>69040.13400000001</v>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>7.296</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>62.459</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>564.856</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>6773.796</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>68360.397</v>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>7.328</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>62.486</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>564.9</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>6652.65</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>68706.412</v>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>7.316</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>62.487</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>564.872</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>6722.551</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>68541.395</v>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>62.484</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>564.746</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>6723.406</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>69279.754</v>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>62.503</v>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>565.015</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>6729.872</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>68835.398</v>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>29.627</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>438.763</v>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 2  —  Promedio y Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>N=400
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>N=400
+Speedup</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>N=800
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>N=800
+Speedup</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>N=1,600
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>N=1,600
+Speedup</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>N=3,200
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>N=3,200
+Speedup</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>N=6,400
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>N=6,400
+Speedup</t>
+        </is>
+      </c>
+      <c r="L69" s="14" t="inlineStr">
+        <is>
+          <t>Speedup
+Prom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>Secuencial naive con O3_full</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="n">
+        <v>30.119</v>
+      </c>
+      <c r="C70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>312.122</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="16" t="n">
+        <v>2543.103</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>35540.429</v>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="16" t="n">
+        <v>399073.004</v>
+      </c>
+      <c r="K70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>Concurrencia 6 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="C71" s="17" t="n">
+        <v>5.6217</v>
+      </c>
+      <c r="D71" s="19" t="n">
+        <v>52.822</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>5.9089</v>
+      </c>
+      <c r="F71" s="19" t="n">
+        <v>429.774</v>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>5.9173</v>
+      </c>
+      <c r="H71" s="19" t="n">
+        <v>6035.98</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>5.8881</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>82004.89200000001</v>
+      </c>
+      <c r="K71" s="17" t="n">
+        <v>4.8665</v>
+      </c>
+      <c r="L71" s="18">
+        <f>IFERROR(AVERAGE(C71,E71,G71,I71,K71),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Concurrencia 12 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>5.722</v>
+      </c>
+      <c r="C72" s="17" t="n">
+        <v>5.2641</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>55.632</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>5.6105</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>436.684</v>
+      </c>
+      <c r="G72" s="17" t="n">
+        <v>5.8237</v>
+      </c>
+      <c r="H72" s="16" t="n">
+        <v>6106.157</v>
+      </c>
+      <c r="I72" s="17" t="n">
+        <v>5.8204</v>
+      </c>
+      <c r="J72" s="16" t="n">
+        <v>82384.681</v>
+      </c>
+      <c r="K72" s="17" t="n">
+        <v>4.844</v>
+      </c>
+      <c r="L72" s="18">
+        <f>IFERROR(AVERAGE(C72,E72,G72,I72,K72),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>OpenMP 12 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C73" s="17" t="n">
+        <v>4.1254</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>62.503</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>4.9937</v>
+      </c>
+      <c r="F73" s="19" t="n">
+        <v>565.015</v>
+      </c>
+      <c r="G73" s="17" t="n">
+        <v>4.5009</v>
+      </c>
+      <c r="H73" s="19" t="n">
+        <v>6729.872</v>
+      </c>
+      <c r="I73" s="17" t="n">
+        <v>5.281</v>
+      </c>
+      <c r="J73" s="19" t="n">
+        <v>68835.398</v>
+      </c>
+      <c r="K73" s="17" t="n">
+        <v>5.7975</v>
+      </c>
+      <c r="L73" s="18">
+        <f>IFERROR(AVERAGE(C73,E73,G73,I73,K73),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Eficiencia paralela  |  sin opt  |  speedup/hilos  |  pthreads vs OpenMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 1  —  Mediciones individuales (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Secuencial naive con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>30.005</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>312.955</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2540.758</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>36022.321</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>434910.671</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>30.071</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>312.064</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2540.398</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>35590.382</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>344113.604</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>30.091</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>312.066</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2550.371</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>35602.554</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>365954.583</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>30.147</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>312.059</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2543.867</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>35751.773</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>334690.484</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>30.083</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>312.649</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2541.859</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>35526.842</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>341364.101</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>30.026</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>311.893</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2546.591</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>35525.175</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>510874.781</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>30.062</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>312.047</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2541.431</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>35557.655</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>505512.386</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>30.237</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>311.989</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2543.702</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>35225.193</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>502152.475</v>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>311.605</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2539.963</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>35261.713</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>325713.787</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>30.227</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>311.89</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2542.086</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>35340.683</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>325443.173</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>30.119</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>312.122</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2543.103</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>35540.429</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>399073.004</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>3.066</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>223.81</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>76245.927</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>19.11</v>
+      </c>
+    </row>
+    <row r="18" ht="6" customHeight="1">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Concurrencia 6 hilos sin optimizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>27.177</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>231.425</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1925.535</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>19635.07</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>181488.392</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>27.103</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>231.266</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>1898.067</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>20025.583</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>183978.726</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>27.247</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>231.623</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>1901.463</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>19810.115</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>184183.954</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>27.055</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>232.311</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1898.751</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>19818.645</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>185783.86</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>26.886</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>231.015</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1900.755</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>20160.773</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>183293.908</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>26.954</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>231.519</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1897.427</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>20028.125</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>181376.852</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>27.357</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>231.937</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1888.214</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>19926.92</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>184224.754</v>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>26.932</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>231.396</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>1905.779</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>19848.389</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>183341.57</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>26.819</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>231.102</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>1901.984</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>19797.74</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>185132.488</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>27.137</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>231.006</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1899.542</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>19979.232</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>183477.022</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>27.067</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>231.46</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1901.752</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>19903.059</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>183628.153</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>9.013</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>143.215</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>1325.197</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="34" ht="6" customHeight="1">
+      <c r="A34" s="12" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Concurrencia 12 hilos sin optimizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>27.135</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>241.861</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>1930.823</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>20183.973</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>226602.819</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>27.523</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>239.888</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1896.905</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>20253.136</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>232067.245</v>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>27.098</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>241.346</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>1885.993</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>20032.987</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>189432.855</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>27.452</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>240.599</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1894.744</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>20011.6</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>186765.113</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>27.533</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>240.538</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>1936.175</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>19980.713</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>188875.706</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>27.471</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>241.95</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>1905.557</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>20052.402</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>189134.831</v>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>27.396</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>243.316</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>1907.132</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>20210.726</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>187229.086</v>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>27.489</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>243.256</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>1897.4</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>20171.908</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>186405.01</v>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>27.182</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>240.299</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>1905.931</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>20018.515</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>185067.773</v>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>27.074</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>240.382</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>1900.956</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>19892.782</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>186407.894</v>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>27.335</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>241.344</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>1906.162</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>20080.874</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>195798.833</v>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>14.957</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>110.749</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>16863.527</v>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>8.609999999999999</v>
+      </c>
+    </row>
+    <row r="50" ht="6" customHeight="1">
+      <c r="A50" s="12" t="n"/>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>OpenMP 12 hilos sin optimizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>17.443</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>1352.007</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>12877.961</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>120547.237</v>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>17.125</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>148.538</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1350.149</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>12830.056</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>119924.839</v>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>17.369</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>148.54</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>1351.256</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>12720.092</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>120046.725</v>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>148.762</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>1350.525</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>12773.513</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>120112.683</v>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>16.458</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>148.501</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>1354.233</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>12732.016</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>120285.409</v>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>17.156</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>148.541</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>1351.538</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>12775.489</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>119644.809</v>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>17.361</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>148.573</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>1352.581</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>12827.217</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>120654.615</v>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>17.491</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>148.575</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>1351.855</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>12758.464</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>120599.122</v>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>17.453</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>148.538</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>1355.596</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>12912.228</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>120680.966</v>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>148.761</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>1350.854</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>12804.143</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>120666.448</v>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>17.272</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>148.59</v>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>1352.059</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>12801.118</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>120316.285</v>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>58.614</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>349.655</v>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 2  —  Promedio y Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>N=400
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>N=400
+Speedup</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>N=800
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>N=800
+Speedup</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>N=1,600
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>N=1,600
+Speedup</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>N=3,200
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>N=3,200
+Speedup</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>N=6,400
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>N=6,400
+Speedup</t>
+        </is>
+      </c>
+      <c r="L69" s="14" t="inlineStr">
+        <is>
+          <t>Speedup
+Prom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>Secuencial naive con O3_full</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="n">
+        <v>30.119</v>
+      </c>
+      <c r="C70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>312.122</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="16" t="n">
+        <v>2543.103</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>35540.429</v>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="16" t="n">
+        <v>399073.004</v>
+      </c>
+      <c r="K70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>Concurrencia 6 hilos sin optimizar</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="n">
+        <v>27.067</v>
+      </c>
+      <c r="C71" s="17" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="D71" s="19" t="n">
+        <v>231.46</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>1.3485</v>
+      </c>
+      <c r="F71" s="19" t="n">
+        <v>1901.752</v>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="H71" s="19" t="n">
+        <v>19903.059</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>1.7857</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>183628.153</v>
+      </c>
+      <c r="K71" s="17" t="n">
+        <v>2.1733</v>
+      </c>
+      <c r="L71" s="18">
+        <f>IFERROR(AVERAGE(C71,E71,G71,I71,K71),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Concurrencia 12 hilos sin optimizar</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>27.335</v>
+      </c>
+      <c r="C72" s="17" t="n">
+        <v>1.1018</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>241.344</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>1.2933</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>1906.162</v>
+      </c>
+      <c r="G72" s="17" t="n">
+        <v>1.3341</v>
+      </c>
+      <c r="H72" s="16" t="n">
+        <v>20080.874</v>
+      </c>
+      <c r="I72" s="17" t="n">
+        <v>1.7699</v>
+      </c>
+      <c r="J72" s="16" t="n">
+        <v>195798.833</v>
+      </c>
+      <c r="K72" s="17" t="n">
+        <v>2.0382</v>
+      </c>
+      <c r="L72" s="18">
+        <f>IFERROR(AVERAGE(C72,E72,G72,I72,K72),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>OpenMP 12 hilos sin optimizar</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n">
+        <v>17.272</v>
+      </c>
+      <c r="C73" s="17" t="n">
+        <v>1.7438</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>148.59</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>2.1006</v>
+      </c>
+      <c r="F73" s="19" t="n">
+        <v>1352.059</v>
+      </c>
+      <c r="G73" s="17" t="n">
+        <v>1.8809</v>
+      </c>
+      <c r="H73" s="19" t="n">
+        <v>12801.118</v>
+      </c>
+      <c r="I73" s="17" t="n">
+        <v>2.7764</v>
+      </c>
+      <c r="J73" s="19" t="n">
+        <v>120316.285</v>
+      </c>
+      <c r="K73" s="17" t="n">
+        <v>3.3169</v>
+      </c>
+      <c r="L73" s="18">
+        <f>IFERROR(AVERAGE(C73,E73,G73,I73,K73),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Eficiencia paralela  |  con O3_full  |  speedup/hilos  |  pthreads vs OpenMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 1  —  Mediciones individuales (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Secuencial naive con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>30.005</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>312.955</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2540.758</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>36022.321</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>434910.671</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>30.071</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>312.064</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2540.398</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>35590.382</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>344113.604</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>30.091</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>312.066</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2550.371</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>35602.554</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>365954.583</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>30.147</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>312.059</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2543.867</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>35751.773</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>334690.484</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>30.083</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>312.649</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2541.859</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>35526.842</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>341364.101</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>30.026</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>311.893</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2546.591</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>35525.175</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>510874.781</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>30.062</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>312.047</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2541.431</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>35557.655</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>505512.386</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>30.237</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>311.989</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2543.702</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>35225.193</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>502152.475</v>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>311.605</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2539.963</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>35261.713</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>325713.787</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>30.227</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>311.89</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2542.086</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>35340.683</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>325443.173</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>30.119</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>312.122</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2543.103</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>35540.429</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>399073.004</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>3.066</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>223.81</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>76245.927</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>19.11</v>
+      </c>
+    </row>
+    <row r="18" ht="6" customHeight="1">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Concurrencia 6 hilos con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>5.364</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>52.811</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>427.681</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>6087.954</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>79986.159</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>52.641</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>430.247</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>6025.668</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>80510.35400000001</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>5.342</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>53.471</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>434.243</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>5995.036</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>82012.837</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>5.391</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>53.033</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>428.75</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>6098.668</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>81003.02800000001</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>5.348</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>429.429</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>6084.622</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>81305.83100000001</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>5.377</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>428.333</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>6049.848</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>81492.15700000001</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>5.346</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>52.736</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>429.682</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>5999.036</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>82822.33</v>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>5.349</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>52.621</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>429.459</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>5956.608</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>84010.095</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>5.359</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>52.484</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>429.73</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>6035.778</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>82918.28999999999</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>5.342</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>52.642</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>430.19</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>6026.583</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>83987.841</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>52.822</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>429.774</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>6035.98</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>82004.89200000001</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>43.273</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>1323.621</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="34" ht="6" customHeight="1">
+      <c r="A34" s="12" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Concurrencia 12 hilos con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>5.449</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>55.774</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>438.728</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>6161.586</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>83248.595</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>5.501</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>55.498</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>436.098</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>6102.139</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>80585.217</v>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>55.289</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>433.324</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>6046.794</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>81627.19</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>5.479</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>55.436</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>434.354</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>6136.767</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>81365.746</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>5.587</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>55.486</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>434.173</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>6067.791</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>84340.577</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>437.879</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>6091.347</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>82143.193</v>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>5.475</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>55.759</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>437.851</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>6079.568</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>81002.622</v>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>5.477</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>55.871</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>437.771</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>6126.084</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>82819.85799999999</v>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>7.812</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>55.922</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>438.506</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>6168.99</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>82459.068</v>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>5.456</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>55.724</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>438.158</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>6080.506</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>84254.745</v>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>5.722</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>55.632</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>436.684</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>6106.157</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>82384.681</v>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>38.666</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>1228.105</v>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="50" ht="6" customHeight="1">
+      <c r="A50" s="12" t="n"/>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>OpenMP 12 hilos con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>7.316</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>62.489</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>564.903</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>6734.835</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>68260.682</v>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>7.286</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>62.479</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>564.923</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>6721.784</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>68969.21400000001</v>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>7.272</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>62.498</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>565.399</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>6748.11</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>68560.27</v>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>7.327</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>62.501</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>565.028</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>6736.491</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>68834.321</v>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>7.298</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>62.489</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>565.646</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>6741.619</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>69801.397</v>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>7.269</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>62.654</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>564.875</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>6743.477</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>69040.13400000001</v>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>7.296</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>62.459</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>564.856</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>6773.796</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>68360.397</v>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>7.328</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>62.486</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>564.9</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>6652.65</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>68706.412</v>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>7.316</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>62.487</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>564.872</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>6722.551</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>68541.395</v>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>62.484</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>564.746</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>6723.406</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>69279.754</v>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>62.503</v>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>565.015</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>6729.872</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>68835.398</v>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>29.627</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>438.763</v>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 2  —  Promedio y Speedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>N=400
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>N=400
+Speedup</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>N=800
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>N=800
+Speedup</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>N=1,600
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>N=1,600
+Speedup</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>N=3,200
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>N=3,200
+Speedup</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>N=6,400
+Avg (ms)</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>N=6,400
+Speedup</t>
+        </is>
+      </c>
+      <c r="L69" s="14" t="inlineStr">
+        <is>
+          <t>Speedup
+Prom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>Secuencial naive con O3_full</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="n">
+        <v>30.119</v>
+      </c>
+      <c r="C70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>312.122</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="16" t="n">
+        <v>2543.103</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>35540.429</v>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="16" t="n">
+        <v>399073.004</v>
+      </c>
+      <c r="K70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>Concurrencia 6 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="n">
+        <v>5.358</v>
+      </c>
+      <c r="C71" s="17" t="n">
+        <v>5.6217</v>
+      </c>
+      <c r="D71" s="19" t="n">
+        <v>52.822</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>5.9089</v>
+      </c>
+      <c r="F71" s="19" t="n">
+        <v>429.774</v>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>5.9173</v>
+      </c>
+      <c r="H71" s="19" t="n">
+        <v>6035.98</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>5.8881</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>82004.89200000001</v>
+      </c>
+      <c r="K71" s="17" t="n">
+        <v>4.8665</v>
+      </c>
+      <c r="L71" s="18">
+        <f>IFERROR(AVERAGE(C71,E71,G71,I71,K71),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Concurrencia 12 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>5.722</v>
+      </c>
+      <c r="C72" s="17" t="n">
+        <v>5.2641</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>55.632</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>5.6105</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>436.684</v>
+      </c>
+      <c r="G72" s="17" t="n">
+        <v>5.8237</v>
+      </c>
+      <c r="H72" s="16" t="n">
+        <v>6106.157</v>
+      </c>
+      <c r="I72" s="17" t="n">
+        <v>5.8204</v>
+      </c>
+      <c r="J72" s="16" t="n">
+        <v>82384.681</v>
+      </c>
+      <c r="K72" s="17" t="n">
+        <v>4.844</v>
+      </c>
+      <c r="L72" s="18">
+        <f>IFERROR(AVERAGE(C72,E72,G72,I72,K72),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>OpenMP 12 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C73" s="17" t="n">
+        <v>4.1254</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>62.503</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>4.9937</v>
+      </c>
+      <c r="F73" s="19" t="n">
+        <v>565.015</v>
+      </c>
+      <c r="G73" s="17" t="n">
+        <v>4.5009</v>
+      </c>
+      <c r="H73" s="19" t="n">
+        <v>6729.872</v>
+      </c>
+      <c r="I73" s="17" t="n">
+        <v>5.281</v>
+      </c>
+      <c r="J73" s="19" t="n">
+        <v>68835.398</v>
+      </c>
+      <c r="K73" s="17" t="n">
+        <v>5.7975</v>
+      </c>
+      <c r="L73" s="18">
+        <f>IFERROR(AVERAGE(C73,E73,G73,I73,K73),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -14392,7 +19202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -14412,7 +19222,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OpenMP vs pthreads  |  sin opt  |  mismos conteos de hilos  |  ref = seq_std/best</t>
+          <t>OpenMP con O3_full  |  Speedup = T(seq_std/best) / T(omp_Nt/best)</t>
         </is>
       </c>
     </row>
@@ -14739,7 +19549,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Concurrencia 6 hilos sin optimizar</t>
+          <t>OpenMP 2 hilos con O3_full</t>
         </is>
       </c>
     </row>
@@ -14780,19 +19590,19 @@
         <v>1</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>27.177</v>
+        <v>42.368</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>231.425</v>
+        <v>375.654</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1925.535</v>
+        <v>3365.843</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>19635.07</v>
+        <v>44539.748</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>181488.392</v>
+        <v>441858.874</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -14800,19 +19610,19 @@
         <v>2</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>27.103</v>
+        <v>42.795</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>231.266</v>
+        <v>373.428</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1898.067</v>
+        <v>3399.33</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>20025.583</v>
+        <v>45124.454</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>183978.726</v>
+        <v>442682.107</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -14820,19 +19630,19 @@
         <v>3</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>27.247</v>
+        <v>42.793</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>231.623</v>
+        <v>375.647</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1901.463</v>
+        <v>3399.988</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>19810.115</v>
+        <v>45940.023</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>184183.954</v>
+        <v>367614.805</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -14840,19 +19650,19 @@
         <v>4</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>27.055</v>
+        <v>42.906</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>232.311</v>
+        <v>370.739</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1898.751</v>
+        <v>3386.435</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>19818.645</v>
+        <v>44369.506</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>185783.86</v>
+        <v>319391.062</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -14860,19 +19670,19 @@
         <v>5</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>26.886</v>
+        <v>42.965</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>231.015</v>
+        <v>369.847</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1900.755</v>
+        <v>3402.383</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>20160.773</v>
+        <v>44669.469</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>183293.908</v>
+        <v>319951.287</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
@@ -14880,19 +19690,19 @@
         <v>6</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>26.954</v>
+        <v>42.899</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>231.519</v>
+        <v>370.643</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1897.427</v>
+        <v>3381.748</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>20028.125</v>
+        <v>44442.842</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>181376.852</v>
+        <v>317749.204</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -14900,19 +19710,19 @@
         <v>7</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>27.357</v>
+        <v>42.566</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>231.937</v>
+        <v>370.707</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1888.214</v>
+        <v>3386.649</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>19926.92</v>
+        <v>44954.395</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>184224.754</v>
+        <v>320654.72</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
@@ -14920,19 +19730,19 @@
         <v>8</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>26.932</v>
+        <v>42.774</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>231.396</v>
+        <v>372.986</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1905.779</v>
+        <v>3389.939</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>19848.389</v>
+        <v>44127.482</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>183341.57</v>
+        <v>315825.38</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -14940,19 +19750,19 @@
         <v>9</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>26.819</v>
+        <v>42.532</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>231.102</v>
+        <v>370.594</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>1901.984</v>
+        <v>3375.46</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>19797.74</v>
+        <v>44501.832</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>185132.488</v>
+        <v>325338.274</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -14960,19 +19770,19 @@
         <v>10</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>27.137</v>
+        <v>42.671</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>231.006</v>
+        <v>370.443</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1899.542</v>
+        <v>3417.749</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>19979.232</v>
+        <v>44585.021</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>183477.022</v>
+        <v>446547.772</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -14982,19 +19792,19 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>27.067</v>
+        <v>42.727</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>231.46</v>
+        <v>372.069</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1901.752</v>
+        <v>3390.552</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>19903.059</v>
+        <v>44725.477</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>183628.153</v>
+        <v>361761.348</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -15004,19 +19814,19 @@
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>0.161</v>
+        <v>0.18</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>0.395</v>
+        <v>2.092</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>9.013</v>
+        <v>14.121</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>143.215</v>
+        <v>485.621</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>1325.197</v>
+        <v>55492.056</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -15026,19 +19836,19 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.72</v>
+        <v>1.09</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.72</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="34" ht="6" customHeight="1">
@@ -15052,7 +19862,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Concurrencia 12 hilos sin optimizar</t>
+          <t>OpenMP 4 hilos con O3_full</t>
         </is>
       </c>
     </row>
@@ -15093,19 +19903,19 @@
         <v>1</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>27.135</v>
+        <v>21.411</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>241.861</v>
+        <v>188.199</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1930.823</v>
+        <v>1694.737</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>20183.973</v>
+        <v>21868.761</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>226602.819</v>
+        <v>221144.552</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
@@ -15113,19 +19923,19 @@
         <v>2</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>27.523</v>
+        <v>20.807</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>239.888</v>
+        <v>163.541</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1896.905</v>
+        <v>1681.684</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>20253.136</v>
+        <v>21875.299</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>232067.245</v>
+        <v>218645.23</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
@@ -15133,19 +19943,19 @@
         <v>3</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>27.098</v>
+        <v>21.439</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>241.346</v>
+        <v>185.091</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>1885.993</v>
+        <v>1694.949</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>20032.987</v>
+        <v>21922.486</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>189432.855</v>
+        <v>220017.236</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
@@ -15153,19 +19963,19 @@
         <v>4</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>27.452</v>
+        <v>21.366</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>240.599</v>
+        <v>186.7</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1894.744</v>
+        <v>1687.458</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>20011.6</v>
+        <v>21920.319</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>186765.113</v>
+        <v>218504.223</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
@@ -15173,19 +19983,19 @@
         <v>5</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>27.533</v>
+        <v>20.538</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>240.538</v>
+        <v>185.833</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>1936.175</v>
+        <v>1692.522</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>19980.713</v>
+        <v>22105.031</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>188875.706</v>
+        <v>217368.822</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
@@ -15193,19 +20003,19 @@
         <v>6</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>27.471</v>
+        <v>21.303</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>241.95</v>
+        <v>185.385</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1905.557</v>
+        <v>1690.845</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>20052.402</v>
+        <v>21879.178</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>189134.831</v>
+        <v>199336.404</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
@@ -15213,19 +20023,19 @@
         <v>7</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>27.396</v>
+        <v>21.303</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>243.316</v>
+        <v>184.867</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>1907.132</v>
+        <v>1682.531</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>20210.726</v>
+        <v>21847.551</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>187229.086</v>
+        <v>200464.745</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
@@ -15233,19 +20043,19 @@
         <v>8</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>27.489</v>
+        <v>21.188</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>243.256</v>
+        <v>185.081</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1897.4</v>
+        <v>1686.737</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>20171.908</v>
+        <v>21868</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>186405.01</v>
+        <v>197083.423</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
@@ -15253,19 +20063,19 @@
         <v>9</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>27.182</v>
+        <v>20.905</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>240.299</v>
+        <v>185.631</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1905.931</v>
+        <v>1687.227</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>20018.515</v>
+        <v>21886.598</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>185067.773</v>
+        <v>198253.884</v>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
@@ -15273,19 +20083,19 @@
         <v>10</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>27.074</v>
+        <v>20.686</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>240.382</v>
+        <v>188.193</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1900.956</v>
+        <v>1685.957</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>19892.782</v>
+        <v>21901.648</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>186407.894</v>
+        <v>198908.991</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
@@ -15295,19 +20105,19 @@
         </is>
       </c>
       <c r="B47" s="9" t="n">
-        <v>27.335</v>
+        <v>21.095</v>
       </c>
       <c r="C47" s="9" t="n">
-        <v>241.344</v>
+        <v>183.852</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1906.162</v>
+        <v>1688.465</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>20080.874</v>
+        <v>21907.487</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>195798.833</v>
+        <v>208972.751</v>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
@@ -15317,19 +20127,19 @@
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>0.179</v>
+        <v>0.314</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1.163</v>
+        <v>6.87</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>14.957</v>
+        <v>4.433</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>110.749</v>
+        <v>69.55</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>16863.527</v>
+        <v>10236.25</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
@@ -15339,19 +20149,19 @@
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>0.66</v>
+        <v>1.49</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>0.48</v>
+        <v>3.74</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.55</v>
+        <v>0.32</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>8.609999999999999</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="50" ht="6" customHeight="1">
@@ -15365,7 +20175,7 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>OpenMP 12 hilos sin optimizar</t>
+          <t>OpenMP 6 hilos con O3_full</t>
         </is>
       </c>
     </row>
@@ -15406,19 +20216,19 @@
         <v>1</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>17.443</v>
+        <v>14.205</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>148.57</v>
+        <v>124.638</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>1352.007</v>
+        <v>1133.425</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>12877.961</v>
+        <v>14630.997</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>120547.237</v>
+        <v>135065.333</v>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
@@ -15426,19 +20236,19 @@
         <v>2</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>17.125</v>
+        <v>14.349</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>148.538</v>
+        <v>124.717</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1350.149</v>
+        <v>1133.236</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>12830.056</v>
+        <v>14628.084</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>119924.839</v>
+        <v>135031.467</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -15446,19 +20256,19 @@
         <v>3</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>17.369</v>
+        <v>14.205</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>148.54</v>
+        <v>124.76</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>1351.256</v>
+        <v>1126.336</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>12720.092</v>
+        <v>14606.231</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>120046.725</v>
+        <v>141699.599</v>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
@@ -15466,19 +20276,19 @@
         <v>4</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>17.51</v>
+        <v>14.374</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>148.762</v>
+        <v>124.831</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1350.525</v>
+        <v>1130.41</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>12773.513</v>
+        <v>14540.141</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>120112.683</v>
+        <v>140334.752</v>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
@@ -15486,19 +20296,19 @@
         <v>5</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>16.458</v>
+        <v>14.37</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>148.501</v>
+        <v>124.633</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1354.233</v>
+        <v>1131.885</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>12732.016</v>
+        <v>14619.816</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>120285.409</v>
+        <v>136563.409</v>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
@@ -15506,19 +20316,19 @@
         <v>6</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>17.156</v>
+        <v>14.366</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>148.541</v>
+        <v>124.712</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1351.538</v>
+        <v>1128.999</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>12775.489</v>
+        <v>14619.765</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>119644.809</v>
+        <v>134982.496</v>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
@@ -15526,19 +20336,19 @@
         <v>7</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>17.361</v>
+        <v>14.316</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>148.573</v>
+        <v>124.716</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1352.581</v>
+        <v>1125.627</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>12827.217</v>
+        <v>14586.914</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>120654.615</v>
+        <v>136343.556</v>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
@@ -15546,19 +20356,19 @@
         <v>8</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>17.491</v>
+        <v>14.354</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>148.575</v>
+        <v>124.773</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1351.855</v>
+        <v>1138.768</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>12758.464</v>
+        <v>14657.505</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>120599.122</v>
+        <v>134439.221</v>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
@@ -15566,19 +20376,19 @@
         <v>9</v>
       </c>
       <c r="B61" s="6" t="n">
-        <v>17.453</v>
+        <v>14.204</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>148.538</v>
+        <v>124.652</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>1355.596</v>
+        <v>1129.223</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>12912.228</v>
+        <v>14673.147</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>120680.966</v>
+        <v>136131.646</v>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
@@ -15586,19 +20396,19 @@
         <v>10</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>17.35</v>
+        <v>14.37</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>148.761</v>
+        <v>124.645</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>1350.854</v>
+        <v>1128.906</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>12804.143</v>
+        <v>14624.914</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>120666.448</v>
+        <v>133763.292</v>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
@@ -15608,19 +20418,19 @@
         </is>
       </c>
       <c r="B63" s="9" t="n">
-        <v>17.272</v>
+        <v>14.311</v>
       </c>
       <c r="C63" s="9" t="n">
-        <v>148.59</v>
+        <v>124.708</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1352.059</v>
+        <v>1130.682</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>12801.118</v>
+        <v>14618.751</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>120316.285</v>
+        <v>136435.477</v>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
@@ -15630,19 +20440,19 @@
         </is>
       </c>
       <c r="B64" s="10" t="n">
-        <v>0.298</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>1.61</v>
+        <v>3.654</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>58.614</v>
+        <v>34.768</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>349.655</v>
+        <v>2451.892</v>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
@@ -15652,272 +20462,982 @@
         </is>
       </c>
       <c r="B65" s="11" t="n">
-        <v>1.73</v>
+        <v>0.5</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.46</v>
+        <v>0.24</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="66" ht="6" customHeight="1">
+      <c r="A66" s="12" t="n"/>
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="12" t="n"/>
+      <c r="D66" s="12" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="12" t="n"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>OpenMP 8 hilos con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>10.625</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>93.48399999999999</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>839.759</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>10875.106</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>105129.709</v>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>10.616</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>843.527</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>10852.801</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>104179.469</v>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>10.614</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>839.659</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>10826.405</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>106173.603</v>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>10.799</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>93.15600000000001</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>839.728</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>10914.293</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>106275.813</v>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>10.693</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>92.893</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>842.158</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>10871.77</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>105254.113</v>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>10.462</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>94.45099999999999</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>841.843</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>10907.212</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>106706.482</v>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>10.624</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>94.16</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>841.2329999999999</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>10972.839</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>104604.647</v>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>10.749</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>91.24299999999999</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>842.288</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>10838.175</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>106244.555</v>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>10.663</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>92.661</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>840.533</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>10829.22</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>106725.565</v>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>10.691</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>92.691</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>843.585</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>10854.596</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>106735.484</v>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>10.654</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>92.681</v>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>841.431</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>10874.242</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>105802.944</v>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="C80" s="10" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>43.453</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>889.905</v>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="82" ht="6" customHeight="1">
+      <c r="A82" s="12" t="n"/>
+      <c r="B82" s="12" t="n"/>
+      <c r="C82" s="12" t="n"/>
+      <c r="D82" s="12" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="12" t="n"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>OpenMP 12 hilos con O3_full</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>N = 400</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>N = 800</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>N = 1,600</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>N = 3,200</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>N = 6,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>7.316</v>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>62.489</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>564.903</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>6734.835</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>68260.682</v>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>7.286</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>62.479</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>564.923</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>6721.784</v>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>68969.21400000001</v>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>7.272</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>62.498</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>565.399</v>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>6748.11</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>68560.27</v>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>7.327</v>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>62.501</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>565.028</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>6736.491</v>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>68834.321</v>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>7.298</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>62.489</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>565.646</v>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>6741.619</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>69801.397</v>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B90" s="7" t="n">
+        <v>7.269</v>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>62.654</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>564.875</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>6743.477</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>69040.13400000001</v>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>7.296</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>62.459</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>564.856</v>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>6773.796</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>68360.397</v>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B92" s="7" t="n">
+        <v>7.328</v>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>62.486</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>564.9</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>6652.65</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>68706.412</v>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>7.316</v>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>62.487</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>564.872</v>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>6722.551</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>68541.395</v>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B94" s="7" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>62.484</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>564.746</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>6723.406</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>69279.754</v>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>62.503</v>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>565.015</v>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>6729.872</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>68835.398</v>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>Desv. Est.</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C96" s="10" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>29.627</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>438.763</v>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>CV (%)</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C97" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Tabla 2  —  Promedio y Speedup</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="13" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>N=400
 Avg (ms)</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>N=400
 Speedup</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>N=800
 Avg (ms)</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>N=800
 Speedup</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>N=1,600
 Avg (ms)</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G101" s="4" t="inlineStr">
         <is>
           <t>N=1,600
 Speedup</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="H101" s="4" t="inlineStr">
         <is>
           <t>N=3,200
 Avg (ms)</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="I101" s="4" t="inlineStr">
         <is>
           <t>N=3,200
 Speedup</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J101" s="4" t="inlineStr">
         <is>
           <t>N=6,400
 Avg (ms)</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="K101" s="4" t="inlineStr">
         <is>
           <t>N=6,400
 Speedup</t>
         </is>
       </c>
-      <c r="L69" s="14" t="inlineStr">
+      <c r="L101" s="14" t="inlineStr">
         <is>
           <t>Speedup
 Prom.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="15" t="inlineStr">
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="15" t="inlineStr">
         <is>
           <t>Secuencial naive con O3_full</t>
         </is>
       </c>
-      <c r="B70" s="16" t="n">
+      <c r="B102" s="16" t="n">
         <v>30.119</v>
       </c>
-      <c r="C70" s="17" t="n">
+      <c r="C102" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D70" s="16" t="n">
+      <c r="D102" s="16" t="n">
         <v>312.122</v>
       </c>
-      <c r="E70" s="17" t="n">
+      <c r="E102" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="16" t="n">
+      <c r="F102" s="16" t="n">
         <v>2543.103</v>
       </c>
-      <c r="G70" s="17" t="n">
+      <c r="G102" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H70" s="16" t="n">
+      <c r="H102" s="16" t="n">
         <v>35540.429</v>
       </c>
-      <c r="I70" s="17" t="n">
+      <c r="I102" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="16" t="n">
+      <c r="J102" s="16" t="n">
         <v>399073.004</v>
       </c>
-      <c r="K70" s="17" t="n">
+      <c r="K102" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="L70" s="18" t="n">
+      <c r="L102" s="18" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="15" t="inlineStr">
-        <is>
-          <t>Concurrencia 6 hilos sin optimizar</t>
-        </is>
-      </c>
-      <c r="B71" s="19" t="n">
-        <v>27.067</v>
-      </c>
-      <c r="C71" s="17" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="D71" s="19" t="n">
-        <v>231.46</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>1.3485</v>
-      </c>
-      <c r="F71" s="19" t="n">
-        <v>1901.752</v>
-      </c>
-      <c r="G71" s="17" t="n">
-        <v>1.3372</v>
-      </c>
-      <c r="H71" s="19" t="n">
-        <v>19903.059</v>
-      </c>
-      <c r="I71" s="17" t="n">
-        <v>1.7857</v>
-      </c>
-      <c r="J71" s="19" t="n">
-        <v>183628.153</v>
-      </c>
-      <c r="K71" s="17" t="n">
-        <v>2.1733</v>
-      </c>
-      <c r="L71" s="18">
-        <f>IFERROR(AVERAGE(C71,E71,G71,I71,K71),"N/A")</f>
+    <row r="103" ht="17" customHeight="1">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>OpenMP 2 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B103" s="19" t="n">
+        <v>42.727</v>
+      </c>
+      <c r="C103" s="17" t="n">
+        <v>0.7049</v>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>372.069</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>0.8389</v>
+      </c>
+      <c r="F103" s="19" t="n">
+        <v>3390.552</v>
+      </c>
+      <c r="G103" s="17" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="H103" s="19" t="n">
+        <v>44725.477</v>
+      </c>
+      <c r="I103" s="17" t="n">
+        <v>0.7946</v>
+      </c>
+      <c r="J103" s="19" t="n">
+        <v>361761.348</v>
+      </c>
+      <c r="K103" s="17" t="n">
+        <v>1.1031</v>
+      </c>
+      <c r="L103" s="18">
+        <f>IFERROR(AVERAGE(C103,E103,G103,I103,K103),"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="15" t="inlineStr">
-        <is>
-          <t>Concurrencia 12 hilos sin optimizar</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="n">
-        <v>27.335</v>
-      </c>
-      <c r="C72" s="17" t="n">
-        <v>1.1018</v>
-      </c>
-      <c r="D72" s="16" t="n">
-        <v>241.344</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>1.2933</v>
-      </c>
-      <c r="F72" s="16" t="n">
-        <v>1906.162</v>
-      </c>
-      <c r="G72" s="17" t="n">
-        <v>1.3341</v>
-      </c>
-      <c r="H72" s="16" t="n">
-        <v>20080.874</v>
-      </c>
-      <c r="I72" s="17" t="n">
-        <v>1.7699</v>
-      </c>
-      <c r="J72" s="16" t="n">
-        <v>195798.833</v>
-      </c>
-      <c r="K72" s="17" t="n">
-        <v>2.0382</v>
-      </c>
-      <c r="L72" s="18">
-        <f>IFERROR(AVERAGE(C72,E72,G72,I72,K72),"N/A")</f>
+    <row r="104" ht="17" customHeight="1">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>OpenMP 4 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="n">
+        <v>21.095</v>
+      </c>
+      <c r="C104" s="17" t="n">
+        <v>1.4278</v>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>183.852</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>1.6977</v>
+      </c>
+      <c r="F104" s="16" t="n">
+        <v>1688.465</v>
+      </c>
+      <c r="G104" s="17" t="n">
+        <v>1.5062</v>
+      </c>
+      <c r="H104" s="16" t="n">
+        <v>21907.487</v>
+      </c>
+      <c r="I104" s="17" t="n">
+        <v>1.6223</v>
+      </c>
+      <c r="J104" s="16" t="n">
+        <v>208972.751</v>
+      </c>
+      <c r="K104" s="17" t="n">
+        <v>1.9097</v>
+      </c>
+      <c r="L104" s="18">
+        <f>IFERROR(AVERAGE(C104,E104,G104,I104,K104),"N/A")</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="15" t="inlineStr">
-        <is>
-          <t>OpenMP 12 hilos sin optimizar</t>
-        </is>
-      </c>
-      <c r="B73" s="19" t="n">
-        <v>17.272</v>
-      </c>
-      <c r="C73" s="17" t="n">
-        <v>1.7438</v>
-      </c>
-      <c r="D73" s="19" t="n">
-        <v>148.59</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>2.1006</v>
-      </c>
-      <c r="F73" s="19" t="n">
-        <v>1352.059</v>
-      </c>
-      <c r="G73" s="17" t="n">
-        <v>1.8809</v>
-      </c>
-      <c r="H73" s="19" t="n">
-        <v>12801.118</v>
-      </c>
-      <c r="I73" s="17" t="n">
-        <v>2.7764</v>
-      </c>
-      <c r="J73" s="19" t="n">
-        <v>120316.285</v>
-      </c>
-      <c r="K73" s="17" t="n">
-        <v>3.3169</v>
-      </c>
-      <c r="L73" s="18">
-        <f>IFERROR(AVERAGE(C73,E73,G73,I73,K73),"N/A")</f>
+    <row r="105" ht="17" customHeight="1">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t>OpenMP 6 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B105" s="19" t="n">
+        <v>14.311</v>
+      </c>
+      <c r="C105" s="17" t="n">
+        <v>2.1046</v>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>124.708</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>2.5028</v>
+      </c>
+      <c r="F105" s="19" t="n">
+        <v>1130.682</v>
+      </c>
+      <c r="G105" s="17" t="n">
+        <v>2.2492</v>
+      </c>
+      <c r="H105" s="19" t="n">
+        <v>14618.751</v>
+      </c>
+      <c r="I105" s="17" t="n">
+        <v>2.4312</v>
+      </c>
+      <c r="J105" s="19" t="n">
+        <v>136435.477</v>
+      </c>
+      <c r="K105" s="17" t="n">
+        <v>2.925</v>
+      </c>
+      <c r="L105" s="18">
+        <f>IFERROR(AVERAGE(C105,E105,G105,I105,K105),"N/A")</f>
         <v/>
       </c>
     </row>
+    <row r="106" ht="17" customHeight="1">
+      <c r="A106" s="15" t="inlineStr">
+        <is>
+          <t>OpenMP 8 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="n">
+        <v>10.654</v>
+      </c>
+      <c r="C106" s="17" t="n">
+        <v>2.8271</v>
+      </c>
+      <c r="D106" s="16" t="n">
+        <v>92.681</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>3.3677</v>
+      </c>
+      <c r="F106" s="16" t="n">
+        <v>841.431</v>
+      </c>
+      <c r="G106" s="17" t="n">
+        <v>3.0224</v>
+      </c>
+      <c r="H106" s="16" t="n">
+        <v>10874.242</v>
+      </c>
+      <c r="I106" s="17" t="n">
+        <v>3.2683</v>
+      </c>
+      <c r="J106" s="16" t="n">
+        <v>105802.944</v>
+      </c>
+      <c r="K106" s="17" t="n">
+        <v>3.7719</v>
+      </c>
+      <c r="L106" s="18">
+        <f>IFERROR(AVERAGE(C106,E106,G106,I106,K106),"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="17" customHeight="1">
+      <c r="A107" s="15" t="inlineStr">
+        <is>
+          <t>OpenMP 12 hilos con O3_full</t>
+        </is>
+      </c>
+      <c r="B107" s="19" t="n">
+        <v>7.301</v>
+      </c>
+      <c r="C107" s="17" t="n">
+        <v>4.1254</v>
+      </c>
+      <c r="D107" s="19" t="n">
+        <v>62.503</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>4.9937</v>
+      </c>
+      <c r="F107" s="19" t="n">
+        <v>565.015</v>
+      </c>
+      <c r="G107" s="17" t="n">
+        <v>4.5009</v>
+      </c>
+      <c r="H107" s="19" t="n">
+        <v>6729.872</v>
+      </c>
+      <c r="I107" s="17" t="n">
+        <v>5.281</v>
+      </c>
+      <c r="J107" s="19" t="n">
+        <v>68835.398</v>
+      </c>
+      <c r="K107" s="17" t="n">
+        <v>5.7975</v>
+      </c>
+      <c r="L107" s="18">
+        <f>IFERROR(AVERAGE(C107,E107,G107,I107,K107),"N/A")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A68:F68"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A100:F100"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15951,7 +21471,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Eficiencia paralela  |  speedup/hilos  |  pthreads vs OpenMP sin opt</t>
+          <t>pthreads/noopt vs OMP/noopt  |  top 2 pthreads + top 1 OMP  |  ref = seq_std/best</t>
         </is>
       </c>
     </row>
